--- a/inventory_full.xlsx
+++ b/inventory_full.xlsx
@@ -3961,7 +3961,7 @@
     <t>NA00705WP</t>
   </si>
   <si>
-    <t>ST-Double sided Latch-KI-W</t>
+    <t>ST-Double sided Latch-KA-W</t>
   </si>
   <si>
     <t>SHCK4T0502</t>
@@ -3976,7 +3976,7 @@
     <t>NA00709WP</t>
   </si>
   <si>
-    <t>ST-Double sided latch-I-B</t>
+    <t>ST-Double sided latch-IK-B</t>
   </si>
   <si>
     <t>SHCK4T0744</t>
@@ -3991,7 +3991,7 @@
     <t>NA00722BP</t>
   </si>
   <si>
-    <t>ST-Double sided latch-kI-B</t>
+    <t>ST-Double sided latch-KA-B</t>
   </si>
   <si>
     <t>SHCK4T0501</t>
@@ -4108,7 +4108,7 @@
     <t>NA00719WP</t>
   </si>
   <si>
-    <t>ST-Single sided latch-B</t>
+    <t>ST-Single sided latch-KA-B</t>
   </si>
   <si>
     <t>SHCK4T0659</t>
@@ -4117,7 +4117,7 @@
     <t>sy://o2/s_qrcode_single/SHCK4T0659</t>
   </si>
   <si>
-    <t>SafeTech SLV-Viper Gravity Latch Single sided (SLV-VIPER-X1)</t>
+    <t>SafeTech SLV-Viper Gravity Latch Single sided (SLV-VIPER-X1) Key Alike</t>
   </si>
   <si>
     <t>NA00726BP</t>
@@ -7807,7 +7807,7 @@
         <v>212</v>
       </c>
       <c r="J41">
-        <v>197</v>
+        <v>186</v>
       </c>
       <c r="K41" t="s">
         <v>34</v>
@@ -7819,7 +7819,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="N41">
-        <v>159.57</v>
+        <v>150.66</v>
       </c>
       <c r="O41" t="b">
         <v>0</v>
@@ -8760,7 +8760,7 @@
         <v>297</v>
       </c>
       <c r="J60">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="K60" t="s">
         <v>34</v>
@@ -8772,7 +8772,7 @@
         <v>26.09</v>
       </c>
       <c r="N60">
-        <v>6105.06</v>
+        <v>5922.43</v>
       </c>
       <c r="O60" t="b">
         <v>0</v>
@@ -9723,7 +9723,7 @@
         <v>368</v>
       </c>
       <c r="AE78" t="s">
-        <v>369</v>
+        <v>68</v>
       </c>
     </row>
     <row r="79" spans="1:32">
